--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_02_19_Cau.xlsx
@@ -848,7 +848,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Assume lần đầu có thể đã ghi một phần, nên replay phải không nhân bản.</t>
+          <t>Khi trang P7 bị timeout sau khi server có thể đã xử lý nhưng client chưa nhận được phản hồi xác nhận: (a) Lưu lại định danh/cursor của P7 kèm số lần thử và thông tin lỗi; (b) Giữ nguyên checkpoint tại trang thành công trước đó (P6); (c) Khi thực hiện replay trang P7 phải sử dụng mã định danh ổn định của từng bản ghi để đảm bảo tính idempotent (không nhân bản dữ liệu nếu server đã ghi một phần). Không được nhảy cóc sang P8.</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: OCR quality không chỉ là một scalar confidence.</t>
+          <t>Các dấu hiệu cảnh báo chất lượng OCR kém cần cách ly (quarantine) để người xem xét trước khi đưa vào embedding: (a) Điểm độ tin cậy thấp (0,42) và xuất hiện nhiều ký tự thay thế lỗi; (b) Ngôn ngữ văn bản bị thay đổi bất thường (từ tiếng Việt sang tiếng Nga); (c) Chiều dài văn bản giảm đột ngột 95% so với các trang tương tự; (e) Bảng dữ liệu bị mất các cột dù số lượng từ ngữ vẫn đủ.</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,11 @@
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
@@ -1041,7 +1045,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính chênh rate rồi nhân thời gian.</t>
+          <t>Tốc độ chênh lệch giữa producer và consumer là: 120 event/s - 90 event/s = 30 event/s. Trong khoảng thời gian 60 giây không co giãn (no scaling), độ sâu hàng đợi (queue depth) tăng thêm là: 30 event/s × 60 s = 1800 event.</t>
         </is>
       </c>
     </row>
@@ -1203,7 +1207,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không replay trước khi biết nguyên nhân vẫn tồn tại.</t>
+          <t>Trình tự xử lý thông điệp độc hại (poison message workflow) với Dead-Letter Queue (DLQ): 1. Consumer tiếp nhận và xử lý message (o2) -&gt; 2. Thử lại có giới hạn (bounded retries) theo điều kiện eligibility (o3) -&gt; 3. Đưa failed event kèm lý do vi phạm và run ID vào DLQ để không chặn nghẽn hàng đợi (o4) -&gt; 4. Kỹ sư kiểm tra, tạo ticket và khắc phục nguyên nhân gốc (o5) -&gt; 5. Replay có chủ đích các message trong DLQ sau khi đã sửa lỗi (o1).</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1382,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Một người khác phải rerun mà không hỏi người sửa.</t>
+          <t>Một quy trình làm sạch dữ liệu được chứng minh là có thể tái lập (replayable) khi thỏa mãn: (a) Dữ liệu thô ban đầu và phiên bản của nó được lưu trữ bất biến; (b) Toàn bộ các quy tắc làm sạch nằm trong mã nguồn và hợp đồng dữ liệu có quản lý phiên bản; (c) Cùng một dữ liệu đầu vào và bộ quy tắc luôn tạo ra cùng một kết quả xác định; (d) Có dấu vết lineage ghi nhận đầy đủ trạng thái trước và sau khi xử lý của từng lần chạy.</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_02_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_02_19_Cau.xlsx
@@ -624,10 +624,19 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tính được delay chưa có nghĩa còn quyền retry.
-Phân tích theo nguyên lý thiết kế: Tính được delay chưa có nghĩa còn quyền retry.</t>
+- [1.5 điểm] Tính toán chính xác candidate delay: 8s + 1.5s = 9.5s theo công thức backoff + jitter.
+- [1.5 điểm] Đưa ra quyết định thực tế chính xác: Không retry do đã cạn kiệt lượt thử (attempt 3/3 = max limit).
+- [1.0 điểm] Nêu rõ quy trình xử lý tiếp theo: log lỗi, fail-fast và chuyển task vào hàng đợi dự phòng/DLQ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Tính Candidate Delay: Theo công thức Exponential Backoff with Additive Jitter:
+   - Base delay = 8.0s
+   - Jitter sample = +1.5s
+   - Candidate delay = Base delay + Jitter sample = 8.0s + 1.5s = 9.5 giây.
+2. Quyết định thực tế theo Attempt Limit: KHÔNG THỰC HIỆN RETRY (Abort / Fail Fast). Lý do: Attempt hiện tại đã là attempt 3 trong giới hạn tối đa 3 lần thử (attempt 3/3). Khi một request đã chạm ngưỡng tối đa (max_attempts = 3) mà vẫn nhận mã HTTP 429 Too Many Requests, quyền retry đã bị cạn kiệt (retry budget exhausted). Pipeline phải lập tức dừng gửi request, ghi nhận lỗi 'RateLimitExceeded (Max retries reached)', đẩy task vào hàng đợi chờ hoặc Dead Letter Queue, và phát cảnh báo để tránh spam upstream API.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc tính toán được candidate delay (9.5s) chỉ là bước xác định thời gian chờ nếu còn quyền thử lại. Tuy nhiên, trong thiết kế hệ thống phân tán chịu lỗi, 'Attempt Limit' (Budget Guardrail) là điều kiện chặn cứng (hard boundary) để ngăn chặn vòng lặp vô hạn và bão retry (retry storm). Ngay khi `current_attempt &gt;= max_attempts`, hệ thống phải chuyển sang trạng thái xử lý lỗi (circuit open / error return), bảo toàn tài nguyên cho các tác vụ khác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+AWS Architecture Blog - Exponential Backoff And Jitter: https://aws.amazon.com/blogs/architecture/exponential-backoff-and-jitter/ và Google Cloud API Design Guide - Retrying Requests: https://cloud.google.com/apis/design/errors#retrying_errors</t>
         </is>
       </c>
     </row>
@@ -748,10 +757,20 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: So danh sách trước và sau insert ở mốc 100.
-Phân tích theo nguyên lý thiết kế: So danh sách trước và sau insert ở mốc 100.</t>
+- [1.5 điểm] Phân tích chính xác cơ chế dịch chuyển chỉ mục gây duplicate (bản ghi 100 thành 101 bị đọc lại ở offset 100) và rủi ro skip khi có biến động dữ liệu.
+- [1.5 điểm] Thiết kế giải pháp Keyset/Cursor-based pagination sử dụng cặp khóa (created_at, id) bất biến kèm cú pháp truy vấn cụ thể.
+- [1.0 điểm] Mô tả rõ cơ chế resume an toàn dựa trên giá trị cursor lưu trong checkpoint.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Giải thích rủi ro Duplicate và Skip:
+   - Rủi ro Duplicate: Khi một dòng mới được chèn ở đầu bảng sau khi page 1 vừa đọc xong, toàn bộ các bản ghi trong database bị dịch chuyển chỉ số xuống 1 đơn vị. Bản ghi thứ 100 (cuối cùng của page 1) giờ đây bị đẩy sang vị trí thứ 101. Khi consumer gọi page 2 với `offset=100`, database sẽ đọc từ bản ghi thứ 101, khiến bản ghi cũ này bị đọc lại lần thứ hai (Duplicate Record).
+   - Rủi ro Skip: Ngược lại, nếu một dòng ở page 1 bị xóa, bản ghi thứ 101 sẽ bị kéo lên vị trí thứ 100 và sẽ bị bỏ sót hoàn toàn khi đọc page 2.
+2. Thiết kế Resume an toàn (Cursor/Keyset Pagination):
+   - Thay thế pagination bằng Keyset Pagination dựa trên trường bất biến có chỉ mục: `WHERE (created_at, id) &lt; (:last_created_at, :last_id) ORDER BY created_at DESC, id DESC LIMIT 100`.
+   - Con trỏ (cursor) lưu trữ cặp giá trị `(created_at, id)` của bản ghi cuối cùng đã xử lý thành công. Khi resume, truy vấn tiếp tục chính xác từ sau mốc con trỏ đó, miễn nhiễm hoàn toàn với việc chèn hoặc xóa bản ghi ở đầu hay giữa bảng.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Offset-based pagination (`OFFSET N LIMIT M`) chỉ hoạt động ổn định trên tập dữ liệu tĩnh tuyệt đối. Trong hệ thống trực tuyến có dữ liệu ghi liên tục, việc dùng offset tạo ra 'cửa sổ trượt không ổn định' (shifting window anomaly). Keyset/Cursor-based pagination giải quyết triệt để vấn đề này bằng cách neo vị trí đọc vào một điểm bất biến trên không gian khóa (deterministic key space), đảm bảo tính lũy tiến và có thể resume an toàn sau sự cố mà không lo trùng lặp hay sót dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Use The Index, Luke! - Keyset Pagination: https://use-the-index-luke.com/no-offset và Martin Kleppmann, Designing Data-Intensive Applications - Secondary Indexes &amp; Cursor Iteration</t>
         </is>
       </c>
     </row>
@@ -924,10 +943,25 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Cùng tên không đồng nghĩa cùng version; khác hash không tự xác định authority.
-Phân tích theo nguyên lý thiết kế: Cùng tên không đồng nghĩa cùng version; khác hash không tự xác định authority.</t>
+- [1.5 điểm] Xây dựng đầy đủ metadata schema chứa các trường cốt lõi: canonical_name, content_hash, source_authority_tier, effective_date, lifecycle_status.
+- [1.5 điểm] Ra quyết định chuẩn xác: H2 là ACTIVE (do nguồn HR portal có thẩm quyền cao và hiệu lực 2026), H1 là SUPERSEDED.
+- [1.0 điểm] Nêu rõ giải pháp bảo đảm an toàn: loại bỏ file superseded khỏi vector index phục vụ RAG và lưu trữ cho audit.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Metadata Schema chuẩn cho tài liệu:
+   - `document_id`: UUID duy nhất cho từng bản thể lưu trữ.
+   - `canonical_name`: Tên định danh logic chuẩn (ví dụ `hr_general_policy`).
+   - `content_hash`: Chuỗi SHA-256 nội dung file (H1, H2) để xác minh tính toàn vẹn.
+   - `source_system`: Nguồn gốc xuất xứ (`hr_portal` vs `email_attachment`).
+   - `source_authority_tier`: Cấp độ thẩm quyền (ví dụ Tier 1: HR Official Portal; Tier 3: Email Personal Inbox).
+   - `effective_date`: Ngày có hiệu lực chính thức (2026-01-01 vs 2024-01-01).
+   - `lifecycle_status`: Trạng thái vòng đời (`ACTIVE`, `SUPERSEDED`, `QUARANTINED`).
+2. Quyết định Active / Superseded:
+   - File H2 từ HR portal (effective 2026): Được đánh dấu `ACTIVE` và đưa vào Vector Index phục vụ RAG. Lý do: HR Portal là nguồn có thẩm quyền cao nhất (Authoritative Source of Truth) và có ngày hiệu lực mới nhất (2026).
+   - File H1 từ email attachment (effective 2024): Được đánh dấu `SUPERSEDED` (hoặc Archived), loại bỏ khỏi active search index để tránh agent trả lời thông tin chính sách cũ đã hết hạn, nhưng vẫn giữ bản ghi trong kho lưu trữ kèm lineage phục vụ audit.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Tên file (`policy.pdf`) và mã băm (`hash`) chỉ là các thuộc tính vật lý, không đại diện cho thẩm quyền nghiệp vụ (business authority) hay tính hiệu lực theo thời gian. Trong quản trị tri thức cho Agent, việc xác định phiên bản hiện hành phải dựa trên 'Hierarchy of Authority' (Thứ bậc thẩm quyền nguồn) và 'Effective Timestamp'. Việc gắn nhãn siêu dữ liệu rõ ràng giúp phân định trạng thái Active/Superseded, ngăn chặn việc mô hình truy hồi phải các chính sách hết hạn được gửi qua email không chính thức.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+DAMA-DMBOK: Data Management Body of Knowledge - Metadata Management and Document Retention Policies; W3C PROV-O Data Lineage Model: https://www.w3.org/TR/prov-o/</t>
         </is>
       </c>
     </row>
@@ -1009,10 +1043,22 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Dữ kiện quyết định nằm ở cấu trúc bị mất, không ở tổng số từ.
-Phân tích theo nguyên lý thiết kế: Dữ kiện quyết định nằm ở cấu trúc bị mất, không ở tổng số từ.</t>
+- [1.0 điểm] Lựa chọn disposition chính xác là QUARANTINE / REJECT (chặn embed, chuyển sang review).
+- [1.5 điểm] Xác định đầy đủ 3 bằng chứng cần lưu trữ: visual gốc, token bounding boxes/confidence map và log lỗi mất cột đơn vị.
+- [1.5 điểm] Định nghĩa rõ ràng tiêu chí nghiệm thu (exit criteria): bảng giá có đầy đủ cột đơn vị được schema validate hoặc có sự xác nhận của con người.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chọn Disposition (Biện pháp xử lý): QUARANTINE / REJECT (Tạm đình chỉ, đưa vào hàng đợi chờ người duyệt - Human-in-the-Loop review). Tuyệt đối KHÔNG xuất bản (publish) hoặc đưa văn bản này vào pipeline tạo embedding cho Vector Database.
+2. Evidence (Bằng chứng) cần giữ lại:
+   - File hình ảnh / PDF gốc của trang văn bản (visual source artifact);
+   - Toàn bộ kết quả OCR text thô kèm bounding box coordinates và confidence map của từng token (.91 overall);
+   - Báo cáo kiểm định cấu trúc (Schema/Table Structural Validation Log) chỉ rõ bảng giá bị mất cột 'đơn vị' (missing mandatory column 'unit').
+3. Exit Criterion (Tiêu chí nghiệm thu) trước khi cho phép embed:
+   - Bảng giá phải được khôi phục đầy đủ cấu trúc: cả cột đơn giá và cột 'đơn vị tính' (VND, USD, triệu đồng...) được trích xuất hoàn chỉnh;
+   - Hoặc (a) Được parser chuyên dụng cho bảng biểu (Table Transformer / PaddleOCR) parse lại thành công và vượt qua schema test, hoặc (b) Được nhân viên nghiệp vụ (Human Reviewer) xác nhận chỉnh sửa và ký duyệt thủ công.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Độ tin cậy tổng thể cao (.91) và độ dài văn bản bình thường là các chỉ số đánh lừa (vanity metrics) trong trích xuất OCR. Việc mất đi một trường mang tính ngữ nghĩa quyết định như 'đơn vị' trong bảng giá là một lỗi nghiêm trọng: 100 nghìn khác 100 triệu. Nếu đưa vào vector database, RAG agent sẽ tạo ra thông tin sai lệch tai hại (hallucination về giá cả). Do đó, quy tắc kiểm định cấu trúc bảng biểu phải đóng vai trò là một 'Hard Quality Gate' chặn dữ liệu trước khi embedding.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google Cloud Document AI Documentation - Handling Table Parsing &amp; Extraction Quality: https://cloud.google.com/document-ai/docs/handle-tables và Great Expectations Table Schema Quality Standards: https://docs.greatexpectations.io/</t>
         </is>
       </c>
     </row>
@@ -1076,10 +1122,24 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ack nào chỉ xác nhận accepted, ack nào xác nhận processed?
-Phân tích theo nguyên lý thiết kế: Ack nào chỉ xác nhận accepted, ack nào xác nhận processed?</t>
+- [1.5 điểm] Phân định chuẩn xác hai ranh giới ack: Producer ack (HTTP 202 sau khi ghi queue) và Consumer ack (chỉ ack sau khi transform thành công).
+- [1.5 điểm] Thiết lập đầy đủ các chỉ số giám sát: API p95/p99 latency, queue depth/lag và worker failure rate.
+- [1.0 điểm] Xây dựng failure policy cụ thể: retry có giới hạn cho transient failure và chuyển sang Dead Letter Queue (DLQ) cho poison pills.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết lập ranh giới Queue và Acknowledgment (Queue/Ack Boundary):
+   - Ingestion Boundary (Producer Side): Webhook API gateway nhận HTTP POST, chỉ thực hiện kiểm tra tính hợp lệ cơ bản (schema validation thô) rồi đẩy ngay message vào một Durable Message Broker (như Kafka / RabbitMQ / AWS SQS). Khi broker trả về 'Message Persisted / Write Ack', Webhook API lập tức phản hồi HTTP 202 Accepted cho đối tác trong vòng &lt; 50ms.
+   - Processing Boundary (Consumer Side): Một nhóm worker chạy nền độc lập (background consumers) pull message từ queue, thực hiện transform tốn 2s. Worker CHỈ gửi Ack / Commit Offset cho broker SAU KHI transformation hoàn tất thành công và lưu kết quả an toàn.
+2. Giám sát (Monitoring):
+   - Ingestion Latency: P95 và P99 response time của Webhook endpoint (&lt; 200ms).
+   - Queue Depth / Consumer Lag: Số lượng message đang tồn đọng trong queue.
+   - Worker Processing Time &amp; Error Rate: Thời gian chạy trung bình của worker và tỷ lệ transform fail.
+3. Chính sách xử lý lỗi (Failure Policy):
+   - Lỗi tạm thời (transient): Retry với Exponential Backoff + Jitter tối đa 3 lần.
+   - Lỗi vĩnh viễn (poison pill / format lỗi): Chuyển message sang Dead Letter Queue (DLQ) kèm toàn bộ stack trace lỗi để phân tích ngoại tuyến mà không làm tắc nghẽn queue chính.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc cốt lõi để đáp ứng SLA độ trễ cao (HTTP 202 trong 200ms) khi tác vụ xử lý tốn nhiều thời gian (2s) là 'Bất đồng bộ hóa qua hàng đợi' (Asynchronous Decoupling). Webhook Ack chỉ xác nhận 'Đã tiếp nhận vào hàng đợi an toàn', trong khi Consumer Ack xác nhận 'Đã xử lý xong nghiệp vụ'. Sự phân tách này bảo vệ hệ thống khỏi quá tải (backpressure protection) và ngăn ngừa mất dữ liệu nếu worker gặp sự cố giữa chừng.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Enterprise Integration Patterns - Message Channel &amp; Guaranteed Delivery: https://www.enterpriseintegrationpatterns.com/patterns/messaging/GuaranteedMessaging.html và Martin Kleppmann, Designing Data-Intensive Applications (O'Reilly)</t>
         </is>
       </c>
     </row>
@@ -1155,10 +1215,21 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tín hiệu cần quay ngược về producer, không chỉ dashboard.
-Phân tích theo nguyên lý thiết kế: Tín hiệu cần quay ngược về producer, không chỉ dashboard.</t>
+- [1.0 điểm] Phân tích đúng số liệu net influx (+80 msg/s) và việc queue depth (9k) đã phá vỡ ngưỡng threshold (5k).
+- [1.5 điểm] Thiết kế kiểm soát backpressure ở 2 đầu: Rate limit/throttling phía producer (HTTP 429 + Retry-After) và Autoscaling phía consumer.
+- [1.5 điểm] Trình bày rõ ràng hệ quả thấy được với người dùng (user-visible consequence): thông báo suy giảm hiệu năng và độ trễ dữ liệu tăng nhưng hệ thống không mất mát dữ liệu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế Control (Hệ thống kiểm soát áp lực ngược - Backpressure Control):
+   - Đánh giá trạng thái: Producer tốc độ 200/s, Consumer tốc độ 120/s -&gt; Net Influx = +80 msg/s. Queue depth tăng vọt từ 1k -&gt; 4k -&gt; 9k trong 3 phút, đã vượt xa ngưỡng an toàn 5k (threshold=5k).
+   - Phía Producer (Admission Control): Kích hoạt cơ chế Rate Limiting / Traffic Throttling tại API Gateway. Áp dụng thuật toán Leaky Bucket / Token Bucket để giảm lưu lượng tiếp nhận từ client xuống mức tối đa 120/s. Khi queue depth &gt; 5k, Gateway trả về HTTP 429 Too Many Requests kèm header `Retry-After: 30` đối với các request không khẩn cấp.
+   - Phía Consumer (Elastic Scaling): Kích hoạt KEDA / Kubernetes HPA scale out số lượng consumer pods dựa trên custom metric `queue_depth &gt; 5000`, tăng từ N replicas lên tối thiểu `ceil(200 / (120/N))` để cân bằng tốc độ xử lý.
+2. Hệ quả hiển thị đối với người dùng (User-Visible Consequence):
+   - Client/Người dùng nhận thông báo trạng thái: 'Hệ thống đang tiếp nhận khối lượng công việc lớn, yêu cầu của bạn đang được xếp hàng xử lý chậm hơn bình thường' (degraded performance SLA).
+   - Các bản ghi mới được gửi lên sẽ có độ trễ cập nhật trên dashboard/agent (freshness lag tăng thêm vài phút) thay vì bị sập hệ thống hoặc mất dữ liệu.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Khi tốc độ sản sinh dữ liệu lớn hơn tốc độ tiêu thụ, nếu không có cơ chế backpressure quay ngược về producer, hàng đợi sẽ tăng vô hạn dẫn đến cạn kiệt bộ nhớ (OOM) hoặc sập broker. Cơ chế backpressure chuẩn mực phải tạo ra 'phản hồi ngược' (feedback loop) từ tầng hàng đợi về tầng ingress để làm chậm hoặc từ chối có kiểm soát các yêu cầu mới, đồng thời tự động co giãn tài nguyên xử lý để đưa queue depth về dưới ngưỡng an toàn.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Reactive Streams Specification - Backpressure Protocol: https://www.reactive-streams.org/ và Kubernetes Event-driven Autoscaling (KEDA) Documentation: https://keda.sh/</t>
         </is>
       </c>
     </row>
@@ -1328,10 +1399,20 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một thay đổi không được mã hóa sẽ biến mất ở lần chạy sau.
-Phân tích theo nguyên lý thiết kế: Một thay đổi không được mã hóa sẽ biến mất ở lần chạy sau.</t>
+- [1.0 điểm] Chẩn đoán chính xác nguyên nhân: chỉnh sửa thủ công ngoài luồng (out-of-band manual edit) không được mã hóa nên bị xóa sạch khi replay.
+- [1.5 điểm] Thiết kế giải pháp chuẩn: cấm sửa canonical, mô hình hóa can thiệp thành bảng/sự kiện hiệu chỉnh (Correction Events / Patch Manifest) có kiểm toán.
+- [1.5 điểm] Tích hợp logic áp dụng patch vào code pipeline để đảm bảo replayability hoàn toàn có tính đơn định (deterministic).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán nguyên nhân sự cố: Vi phạm tính đơn định và khả năng tái lập (Violation of Deterministic Replayability). Dữ liệu canonical bị can thiệp chỉnh sửa thủ công trực tiếp trên CSV (manual out-of-band edit). Thay đổi này không được mã hóa thành code, rule hay migration script và không được lưu vào kho lưu trữ raw/audit. Khi Run B được kích hoạt lại từ raw data bằng code v3, toàn bộ dữ liệu canonical bị tạo lại từ đầu (recomputed from scratch), dẫn đến mọi chỉnh sửa tay biến mất hoàn toàn.
+2. Thiết kế cơ chế Replay và Audit đúng chuẩn:
+   - Cấm hoàn toàn sửa trực tiếp vào file canonical (Immutable Canonical Layer).
+   - Mô hình hóa can thiệp con người dưới dạng 'Correction Event' trong kho lưu trữ dữ liệu thô: Tạo bảng `manual_corrections` hoặc `patch_manifest` (lưu: `record_id`, `field_name`, `old_value`, `new_value`, `reason`, `operator_id`, `approved_by`, `timestamp`).
+   - Tích hợp logic áp dụng patch vào pipeline code v4: Sau khi clean tự động, pipeline tự động join với `manual_corrections` để đè các trường đã được phê duyệt.
+   - Audit Trail: Bất kỳ lần Replay nào (Run C, Run D) từ raw + correction events đều tạo ra kết quả đồng nhất tuyệt đối (deterministic idempotency).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kỹ nghệ dữ liệu hiện đại, nguyên lý 'Code as Configuration' và 'Data Immutability' quy định rằng mọi trạng thái của dữ liệu phái sinh phải là một hàm thuần túy (pure function) của Dữ liệu thô và Mã xử lý: `Canonical = f(Raw, Code)`. Nếu có sự tham gia của con người để sửa sai, hành động đó phải được coi như một luồng dữ liệu đầu vào bổ sung (Data Patch / Correction Event) có version control và audit log đầy đủ, chứ không bao giờ được chỉnh sửa trực tiếp vào tầng serving.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Kleppmann, Designing Data-Intensive Applications - Reproducibility, Immutability &amp; Event Sourcing; DataOps Principles: https://dataopsmanifesto.org/</t>
         </is>
       </c>
     </row>
